--- a/projects/ai-core/doc/data/res_syn_area.xlsx
+++ b/projects/ai-core/doc/data/res_syn_area.xlsx
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="60">
-  <si>
-    <t xml:space="preserve">Synthesis Cell Area — Baseline / Square / BFP / Square-BFP / Bit-Plane-A BFP, ASAP7 RVT/TT (analytic from 2x2)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="66">
+  <si>
+    <t xml:space="preserve">Synthesis Cell Area — Baseline / Square / BFP / Square-BFP / Bit-Plane-A BFP / NR4SD BFP, ASAP7 RVT/TT (analytic from 2x2)</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -179,6 +179,18 @@
     <t xml:space="preserve">Bit-Plane-B BFP total </t>
   </si>
   <si>
+    <t xml:space="preserve">NR4SD BFP — top_NxN_nr4sd_bfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disp_array_b_nr4sd_bfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pe_nr4sd_bfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR4SD BFP total </t>
+  </si>
+  <si>
     <t xml:space="preserve">Square / Baseline </t>
   </si>
   <si>
@@ -201,6 +213,12 @@
   </si>
   <si>
     <t xml:space="preserve">Bit-Plane-B BFP / BFP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR4SD BFP / Baseline </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR4SD BFP / BFP</t>
   </si>
 </sst>
 </file>
@@ -448,13 +466,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:I85"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B1:I99"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="4" style="1" width="24.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="1" width="30.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2126,135 +2143,429 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="10" t="n">
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B79" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>8.87922</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>3.41172</v>
+      </c>
+      <c r="G79" s="8" t="n">
+        <v>5.4675</v>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>8.879</v>
+      </c>
+      <c r="I79" s="8" t="n">
+        <v>8.879</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B80" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>277.73442</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>97.04448</v>
+      </c>
+      <c r="G80" s="8" t="n">
+        <v>180.68994</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>2221.875</v>
+      </c>
+      <c r="I80" s="8" t="n">
+        <v>4443.751</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B81" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>526.90662</v>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>97.044</v>
+      </c>
+      <c r="G81" s="8" t="n">
+        <v>429.8621</v>
+      </c>
+      <c r="H81" s="8" t="n">
+        <v>4215.253</v>
+      </c>
+      <c r="I81" s="8" t="n">
+        <v>8430.506</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B82" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>42.92352</v>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>9.09792</v>
+      </c>
+      <c r="G82" s="8" t="n">
+        <v>33.8256</v>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>343.388</v>
+      </c>
+      <c r="I82" s="8" t="n">
+        <v>686.776</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B83" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="7" t="n">
+        <v>75.17448</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>18.19584</v>
+      </c>
+      <c r="G83" s="8" t="n">
+        <v>56.97864</v>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>601.396</v>
+      </c>
+      <c r="I83" s="8" t="n">
+        <v>1202.792</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B84" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>4659.4035</v>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>424.57</v>
+      </c>
+      <c r="G84" s="8" t="n">
+        <v>4234.8339</v>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>298201.824</v>
+      </c>
+      <c r="I84" s="8" t="n">
+        <v>1192807.296</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B85" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="8" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>16.796</v>
+      </c>
+      <c r="I85" s="8" t="n">
+        <v>67.185</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="8" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>4.199</v>
+      </c>
+      <c r="I86" s="8" t="n">
+        <v>8.398</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="7" t="n">
+        <v>1.25388</v>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="8" t="n">
+        <v>1.2539</v>
+      </c>
+      <c r="H87" s="8" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="I87" s="8" t="n">
+        <v>1.254</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="9"/>
+      <c r="H88" s="10" t="n">
+        <v>305614.864</v>
+      </c>
+      <c r="I88" s="10" t="n">
+        <v>1207656.837</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="9"/>
+      <c r="H90" s="10" t="n">
         <v>0.9905</v>
       </c>
-      <c r="I78" s="10" t="n">
+      <c r="I90" s="10" t="n">
         <v>0.931</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B79" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="10" t="n">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
+      <c r="G91" s="9"/>
+      <c r="H91" s="10" t="n">
         <v>1.3949</v>
       </c>
-      <c r="I79" s="10" t="n">
+      <c r="I91" s="10" t="n">
         <v>1.3978</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B80" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="10" t="n">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="9"/>
+      <c r="H92" s="10" t="n">
         <v>1.4307</v>
       </c>
-      <c r="I80" s="10" t="n">
+      <c r="I92" s="10" t="n">
         <v>1.3976</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B81" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="10" t="n">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="10" t="n">
         <v>1.0256</v>
       </c>
-      <c r="I81" s="10" t="n">
+      <c r="I93" s="10" t="n">
         <v>0.9999</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B82" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="10" t="n">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9"/>
+      <c r="G94" s="9"/>
+      <c r="H94" s="10" t="n">
         <v>1.3493</v>
       </c>
-      <c r="I82" s="10" t="n">
+      <c r="I94" s="10" t="n">
         <v>1.3492</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B83" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="10" t="n">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="10" t="n">
         <v>0.9673</v>
       </c>
-      <c r="I83" s="10" t="n">
+      <c r="I95" s="10" t="n">
         <v>0.9652</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B84" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="10" t="n">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="9"/>
+      <c r="F96" s="9"/>
+      <c r="G96" s="9"/>
+      <c r="H96" s="10" t="n">
         <v>1.2042</v>
       </c>
-      <c r="I84" s="10" t="n">
+      <c r="I96" s="10" t="n">
         <v>1.2028</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B85" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="10" t="n">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="9"/>
+      <c r="H97" s="10" t="n">
         <v>0.8633</v>
       </c>
-      <c r="I85" s="10" t="n">
+      <c r="I97" s="10" t="n">
         <v>0.8605</v>
       </c>
     </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="10" t="n">
+        <v>1.2213</v>
+      </c>
+      <c r="I98" s="10" t="n">
+        <v>1.2211</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="10" t="n">
+        <v>0.8755</v>
+      </c>
+      <c r="I99" s="10" t="n">
+        <v>0.8736</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="25">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B12:G12"/>
@@ -2268,14 +2579,18 @@
     <mergeCell ref="B64:G64"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B78:G78"/>
-    <mergeCell ref="B79:G79"/>
-    <mergeCell ref="B80:G80"/>
-    <mergeCell ref="B81:G81"/>
-    <mergeCell ref="B82:G82"/>
-    <mergeCell ref="B83:G83"/>
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="B85:G85"/>
+    <mergeCell ref="B78:I78"/>
+    <mergeCell ref="B88:G88"/>
+    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="B91:G91"/>
+    <mergeCell ref="B92:G92"/>
+    <mergeCell ref="B93:G93"/>
+    <mergeCell ref="B94:G94"/>
+    <mergeCell ref="B95:G95"/>
+    <mergeCell ref="B96:G96"/>
+    <mergeCell ref="B97:G97"/>
+    <mergeCell ref="B98:G98"/>
+    <mergeCell ref="B99:G99"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
